--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.3118150692149</v>
+        <v>4.763169948747422</v>
       </c>
       <c r="D2" t="n">
-        <v>29.18483639615848</v>
+        <v>4.742535914375754</v>
       </c>
       <c r="E2" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F2" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.07187615242323</v>
+        <v>2.286679874768775</v>
       </c>
       <c r="D3" t="n">
-        <v>13.84708382260917</v>
+        <v>2.25015112117399</v>
       </c>
       <c r="E3" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F3" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.94306828621805</v>
+        <v>6.003248596510433</v>
       </c>
       <c r="D4" t="n">
-        <v>36.47771062860198</v>
+        <v>5.927627977147822</v>
       </c>
       <c r="E4" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F4" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.85895757737858</v>
+        <v>5.50208060632402</v>
       </c>
       <c r="D5" t="n">
-        <v>33.45918791457426</v>
+        <v>5.437118036118317</v>
       </c>
       <c r="E5" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F5" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.21692694367127</v>
+        <v>10.59775062834658</v>
       </c>
       <c r="D6" t="n">
-        <v>65.6383931205127</v>
+        <v>10.66623888208331</v>
       </c>
       <c r="E6" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F6" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>80.03785738057928</v>
+        <v>13.00615182434413</v>
       </c>
       <c r="D7" t="n">
-        <v>79.76117711246731</v>
+        <v>12.96119128077594</v>
       </c>
       <c r="E7" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F7" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.90386120405491</v>
+        <v>3.559377445658922</v>
       </c>
       <c r="D8" t="n">
-        <v>21.19442584309235</v>
+        <v>3.444094199502508</v>
       </c>
       <c r="E8" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F8" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.80321977712248</v>
+        <v>2.893023213782404</v>
       </c>
       <c r="D9" t="n">
-        <v>18.6367710425815</v>
+        <v>3.028475294419494</v>
       </c>
       <c r="E9" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F9" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.45104515075322</v>
+        <v>5.598294836997398</v>
       </c>
       <c r="D10" t="n">
-        <v>34.01497841731351</v>
+        <v>5.527433992813445</v>
       </c>
       <c r="E10" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F10" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>72.02570616051621</v>
+        <v>11.70417725108388</v>
       </c>
       <c r="D11" t="n">
-        <v>72.90937775592789</v>
+        <v>11.84777388533828</v>
       </c>
       <c r="E11" t="n">
-        <v>22.23943861396603</v>
+        <v>3.613908774769481</v>
       </c>
       <c r="F11" t="n">
-        <v>22.40684998153837</v>
+        <v>3.641113121999986</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
